--- a/data/trans_dic/P02E$contratada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 9,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,69</t>
+          <t>1,04; 9,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 7,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 14,9</t>
+          <t>3,39; 14,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,66</t>
+          <t>0,95; 8,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,63</t>
+          <t>2,99; 10,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,5</t>
+          <t>0,58; 5,21</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,99</t>
+          <t>0,0; 8,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,0</t>
+          <t>1,25; 8,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,07</t>
+          <t>0,57; 5,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,51</t>
+          <t>0,28; 2,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,8</t>
+          <t>0,63; 5,45</t>
         </is>
       </c>
     </row>
@@ -898,42 +898,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,05</t>
+          <t>0,0; 8,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 7,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,74</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,1</t>
+          <t>1,02; 5,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,82</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,7</t>
+          <t>0,63; 3,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,34</t>
+          <t>0,5; 4,76</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 30,68</t>
+          <t>2,73; 30,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,58</t>
+          <t>0,0; 18,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 15,07</t>
+          <t>1,42; 16,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,73</t>
+          <t>0,0; 13,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 14,69</t>
+          <t>2,43; 15,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,89</t>
+          <t>0,65; 8,06</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,91</t>
+          <t>1,27; 12,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,41</t>
+          <t>0,0; 11,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 12,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,74</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,78</t>
+          <t>0,82; 7,1</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,04</t>
+          <t>0,47; 5,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,44</t>
+          <t>1,04; 4,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,06</t>
+          <t>0,47; 4,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,09</t>
+          <t>1,03; 4,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,59</t>
+          <t>0,64; 3,61</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 8,58</t>
+          <t>0,76; 8,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,41</t>
+          <t>0,48; 4,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,46</t>
+          <t>0,59; 6,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,04</t>
+          <t>1,08; 5,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,55</t>
+          <t>1,16; 5,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,18; 1,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,82</t>
+          <t>1,06; 3,82</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,23</t>
+          <t>0,85; 3,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,8</t>
+          <t>0,97; 2,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,69</t>
+          <t>1,39; 3,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>1,04; 2,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,78</t>
+          <t>1,26; 2,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,03</t>
+          <t>1,3; 3,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,57</t>
+          <t>1,16; 2,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,47</t>
+          <t>1,31; 2,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,94</t>
+          <t>1,61; 2,98</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5536</t>
+          <t>0; 5859</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>976; 8615</t>
+          <t>926; 8474</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5311</t>
+          <t>0; 5323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2126</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4749; 21007</t>
+          <t>4774; 19877</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>933; 7566</t>
+          <t>935; 8091</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6859</t>
+          <t>0; 6066</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7797; 24446</t>
+          <t>6863; 24345</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1004; 9496</t>
+          <t>1004; 8998</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4839</t>
+          <t>0; 4770</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6383</t>
+          <t>0; 6606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1195; 12414</t>
+          <t>1729; 12017</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6554</t>
+          <t>0; 8084</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7326</t>
+          <t>0; 7521</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>998; 12569</t>
+          <t>1179; 11760</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>950; 8576</t>
+          <t>946; 8202</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1092; 10269</t>
+          <t>1349; 11673</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1932</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5418</t>
+          <t>0; 5021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6577</t>
+          <t>0; 7504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 8730</t>
+          <t>0; 8761</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7013</t>
+          <t>0; 6605</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7274</t>
+          <t>0; 7850</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 9064</t>
+          <t>0; 8968</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>900; 7790</t>
+          <t>897; 7793</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5259</t>
+          <t>0; 5637</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2110</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2023</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1850</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1866; 11038</t>
+          <t>1836; 10165</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>873; 8078</t>
+          <t>0; 7823</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5859</t>
+          <t>0; 4863</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1855; 10805</t>
+          <t>1853; 10510</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 7720</t>
+          <t>890; 8455</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>849; 9509</t>
+          <t>846; 9475</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 10754</t>
+          <t>0; 10127</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1549; 10916</t>
+          <t>1030; 11697</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 8331</t>
+          <t>0; 7387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2059; 12332</t>
+          <t>2036; 13111</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 12303</t>
+          <t>0; 11082</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1018; 10779</t>
+          <t>1021; 12600</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6675</t>
+          <t>0; 6057</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>794; 7476</t>
+          <t>796; 7750</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7209</t>
+          <t>0; 8214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 7529</t>
+          <t>0; 8457</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7397</t>
+          <t>0; 7987</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6644</t>
+          <t>0; 5783</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1241; 10327</t>
+          <t>1095; 9421</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4507</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1059; 12975</t>
+          <t>1012; 12586</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7913</t>
+          <t>0; 7666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5000</t>
+          <t>0; 4457</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2208; 12591</t>
+          <t>2959; 13548</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>952; 8276</t>
+          <t>960; 8422</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6178</t>
+          <t>0; 6404</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5252; 20377</t>
+          <t>5126; 20421</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2019; 11718</t>
+          <t>2081; 11785</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1040; 11596</t>
+          <t>1031; 11815</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5700</t>
+          <t>0; 6025</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928; 9973</t>
+          <t>1084; 9620</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1167; 12723</t>
+          <t>1164; 12223</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 8027</t>
+          <t>0; 7921</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3461; 16221</t>
+          <t>3470; 16675</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3857; 18425</t>
+          <t>3865; 18196</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>943; 10043</t>
+          <t>1042; 9370</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5983; 20912</t>
+          <t>5813; 20931</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5288; 20210</t>
+          <t>5347; 19648</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9777; 27556</t>
+          <t>9537; 27679</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10375; 27925</t>
+          <t>10492; 28417</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9755; 28288</t>
+          <t>10421; 28616</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18523; 42096</t>
+          <t>19166; 41051</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14305; 33665</t>
+          <t>14456; 34645</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17969; 41980</t>
+          <t>18906; 41571</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>33115; 61772</t>
+          <t>32835; 61688</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29124; 54874</t>
+          <t>30033; 55725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Provincia-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,05</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,53</t>
+          <t>1,07; 9,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,21</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 14,1</t>
+          <t>3,62; 13,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,19</t>
+          <t>0,93; 7,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,59</t>
+          <t>3,35; 10,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,21</t>
+          <t>0,57; 5,32</t>
         </is>
       </c>
     </row>
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,71</t>
+          <t>0,87; 8,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,68</t>
+          <t>0,58; 5,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,4</t>
+          <t>0,28; 2,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,45</t>
+          <t>0,5; 5,11</t>
         </is>
       </c>
     </row>
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,39</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,13</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 8,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,56</t>
+          <t>0,64; 5,53</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,62</t>
+          <t>1,07; 6,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,73; 6,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,6</t>
+          <t>0,68; 3,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,76</t>
+          <t>0,49; 4,73</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 30,57</t>
+          <t>2,75; 30,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,43</t>
+          <t>0,0; 19,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 16,15</t>
+          <t>2,26; 14,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 15,62</t>
+          <t>2,47; 15,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,06</t>
+          <t>0,65; 7,53</t>
         </is>
       </c>
     </row>
@@ -1233,17 +1233,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,38</t>
+          <t>0,0; 7,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,35</t>
+          <t>1,27; 12,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,86</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,09</t>
+          <t>0,0; 8,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,1</t>
+          <t>0,92; 7,59</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,86</t>
+          <t>0,9; 6,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,78</t>
+          <t>1,04; 4,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,13</t>
+          <t>0,47; 4,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,1</t>
+          <t>1,2; 4,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,61</t>
+          <t>0,62; 3,47</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,74</t>
+          <t>0,76; 9,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,25</t>
+          <t>0,42; 3,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,21</t>
+          <t>0,83; 6,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,18</t>
+          <t>1,12; 4,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,48</t>
+          <t>1,23; 5,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,65</t>
+          <t>0,18; 1,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,82</t>
+          <t>1,19; 3,94</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,14</t>
+          <t>0,92; 3,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>0,99; 2,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,76</t>
+          <t>1,52; 3,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,85</t>
+          <t>0,99; 2,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,71</t>
+          <t>1,25; 2,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,12</t>
+          <t>1,25; 3,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,55</t>
+          <t>1,19; 2,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,47</t>
+          <t>1,29; 2,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,98</t>
+          <t>1,55; 2,92</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5859</t>
+          <t>0; 6199</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>926; 8474</t>
+          <t>949; 8728</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5323</t>
+          <t>0; 5043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4774; 19877</t>
+          <t>5104; 19156</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>935; 8091</t>
+          <t>919; 7598</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6066</t>
+          <t>0; 6148</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6863; 24345</t>
+          <t>7701; 24565</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1004; 8998</t>
+          <t>991; 9177</t>
         </is>
       </c>
     </row>
@@ -2029,42 +2029,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4770</t>
+          <t>0; 4778</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6606</t>
+          <t>0; 7417</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1729; 12017</t>
+          <t>1203; 11997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8084</t>
+          <t>0; 7418</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7521</t>
+          <t>0; 7833</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1179; 11760</t>
+          <t>1197; 12185</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>946; 8202</t>
+          <t>940; 7573</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1349; 11673</t>
+          <t>1075; 10943</t>
         </is>
       </c>
     </row>
@@ -2197,37 +2197,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5021</t>
+          <t>0; 4999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7504</t>
+          <t>0; 7333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 8761</t>
+          <t>0; 8048</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6605</t>
+          <t>0; 6642</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7850</t>
+          <t>0; 7522</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 8968</t>
+          <t>0; 8575</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>897; 7793</t>
+          <t>898; 7753</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5637</t>
+          <t>0; 5203</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2370,27 +2370,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1836; 10165</t>
+          <t>1938; 11345</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7823</t>
+          <t>871; 7705</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4863</t>
+          <t>0; 4922</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1853; 10510</t>
+          <t>1978; 10900</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>890; 8455</t>
+          <t>877; 8409</t>
         </is>
       </c>
     </row>
@@ -2513,22 +2513,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>846; 9475</t>
+          <t>852; 9527</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 10127</t>
+          <t>0; 10464</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1030; 11697</t>
+          <t>1635; 10845</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 7387</t>
+          <t>0; 7390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2036; 13111</t>
+          <t>2076; 12738</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 11082</t>
+          <t>0; 10870</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1021; 12600</t>
+          <t>1009; 11777</t>
         </is>
       </c>
     </row>
@@ -2681,17 +2681,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6057</t>
+          <t>0; 6507</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>796; 7750</t>
+          <t>799; 7674</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 8214</t>
+          <t>0; 6937</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 8457</t>
+          <t>0; 6237</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7987</t>
+          <t>0; 7889</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5783</t>
+          <t>0; 7609</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1095; 9421</t>
+          <t>1217; 10075</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4235</t>
+          <t>0; 4288</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1012; 12586</t>
+          <t>1933; 13140</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7666</t>
+          <t>0; 6644</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4457</t>
+          <t>0; 5444</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2959; 13548</t>
+          <t>2946; 13273</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>960; 8422</t>
+          <t>965; 8390</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6404</t>
+          <t>0; 5908</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5126; 20421</t>
+          <t>5994; 20538</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2081; 11785</t>
+          <t>2012; 11307</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1031; 11815</t>
+          <t>1027; 12345</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6025</t>
+          <t>0; 6594</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1084; 9620</t>
+          <t>954; 8999</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1164; 12223</t>
+          <t>1634; 12315</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7921</t>
+          <t>0; 8044</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3470; 16675</t>
+          <t>3608; 15676</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3865; 18196</t>
+          <t>4095; 17410</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1042; 9370</t>
+          <t>1025; 9879</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5813; 20931</t>
+          <t>6541; 21598</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5347; 19648</t>
+          <t>5776; 21178</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9537; 27679</t>
+          <t>9748; 28174</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10492; 28417</t>
+          <t>11538; 27798</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10421; 28616</t>
+          <t>9967; 28037</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19166; 41051</t>
+          <t>19027; 41013</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14456; 34645</t>
+          <t>13903; 33511</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18906; 41571</t>
+          <t>19499; 43188</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>32835; 61688</t>
+          <t>32198; 61828</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30033; 55725</t>
+          <t>28981; 54461</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
